--- a/WebMap30-04.xlsx
+++ b/WebMap30-04.xlsx
@@ -1,35 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28609"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walke\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAEDC214-6647-477B-9FB1-C1CF3C428828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="10860" yWindow="0" windowWidth="12276" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="a1MDjRRK1kkpdKMtZfQ8fOCNTB1P+JPb50jyAZfUjlI="/>
     </ext>
   </extLst>
 </workbook>
@@ -62,7 +42,7 @@
     <t>UNDP Afghanistan strengthens resilience amid hardship</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/54073565836/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/54073565836_7122c70a27_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-afghanistan-strengthens-resilience-amid-hardship</t>
@@ -98,7 +78,7 @@
     <t>UNDP Cameroon goes green</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53998772061/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53998772061_f54d2f282e_b.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-cameroon-goes-green</t>
@@ -110,7 +90,7 @@
     <t>UNDP China pursues threefold approach for climate resilience</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53999078704/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53999078704_c4f822dbb5_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-china-pursues-threefold-approach-for-climate-resilience</t>
@@ -122,7 +102,7 @@
     <t>UNDP Cuba leading efforts to create energy resilience</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53998766761/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53998766761_ca695363c7_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-cuba-leading-efforts-to-create-energy-resilience</t>
@@ -182,7 +162,7 @@
     <t>Advancing energy efficiency at UNDP Iran</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53998986808/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53998986808_9210af26c1_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/advancing-energy-efficiency-at-undp-iran</t>
@@ -219,7 +199,7 @@
 *All references to Kosovo shall be understood to be in the context of the Security Council Resolution 1244 (1999).</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53999122989/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53999122989_127a8a109c_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-kosovo-is-walking-the-talk</t>
@@ -249,7 +229,7 @@
     <t>Transitioning UNDP Malawi to a greener future</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53999083179/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53999083179_dab83bd105_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/transitioning-undp-malawi-to-a-greener-future</t>
@@ -324,7 +304,7 @@
     <t>Accelerating Samoa’s green energy transition</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53999000388/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53999000388_9e57c4d530_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/accelerating-samoas-green-energy-transition</t>
@@ -345,7 +325,7 @@
     <t>UNDP Sri Lanka empowering resilience through solar</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53997881757/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53997881757_311be5bc9d_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-sri-lanka-empowering-resilience-through-solar</t>
@@ -357,7 +337,7 @@
     <t>UNDP Syria drives energy resilience</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53998981933/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53998981933_9e138667a4_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-syria-drives-energy-resilience</t>
@@ -387,7 +367,7 @@
     <t>UNDP Ukraine adopts green energy</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53999261250/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53999261250_6f5e0091c7_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-ukraine-adopts-green-energy</t>
@@ -408,7 +388,7 @@
     <t>UNDP Viet Nam enhances sustainable energy use</t>
   </si>
   <si>
-    <t>https://www.flickr.com/photos/undpclimatechangeadaptation/53998736966/in/album-72177720320376554</t>
+    <t>https://live.staticflickr.com/65535/53998736966_d63bbc6d36_w.jpg</t>
   </si>
   <si>
     <t>https://undpgreeningmoonshot.exposure.co/undp-viet-nam-enhances-sustainable-energy-use</t>
@@ -426,30 +406,55 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="9">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -457,62 +462,64 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+  <cellXfs count="9">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="5B9BD5"/>
@@ -536,79 +543,19 @@
         <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -749,29 +696,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="4" width="59.7109375" customWidth="1"/>
-    <col min="5" max="5" width="51.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="21.86"/>
+    <col customWidth="1" min="2" max="2" width="17.0"/>
+    <col customWidth="1" min="3" max="4" width="59.71"/>
+    <col customWidth="1" min="5" max="5" width="51.71"/>
+    <col customWidth="1" min="6" max="6" width="8.71"/>
+    <col customWidth="1" min="7" max="7" width="26.29"/>
+    <col customWidth="1" min="8" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -791,826 +735,1533 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
+    <row r="7" ht="14.25" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+    <row r="9" ht="14.25" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
+    <row r="13" ht="14.25" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="43.15">
-      <c r="A16" t="s">
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
+    <row r="20" ht="14.25" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
+    <row r="21" ht="14.25" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
+    <row r="22" ht="14.25" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
+    <row r="23" ht="14.25" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
+    <row r="24" ht="14.25" customHeight="1">
+      <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
+    <row r="25" ht="14.25" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
+    <row r="26" ht="14.25" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
+    <row r="27" ht="14.25" customHeight="1">
+      <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
+    <row r="28" ht="14.25" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
+    <row r="29" ht="14.25" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="A30" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="5" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="5" t="s">
         <v>127</v>
       </c>
     </row>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B38">
-    <sortCondition ref="B2:B38"/>
-  </sortState>
   <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" xr:uid="{08123BFA-C234-4DB2-B843-B6E9A313A91B}"/>
-    <hyperlink ref="E9" r:id="rId2" xr:uid="{1F3C274F-DE72-413F-A2F4-6B5BBDA53F29}"/>
-    <hyperlink ref="E13" r:id="rId3" xr:uid="{8C1BF79F-ED3D-4BE4-882B-B1732ABC495B}"/>
-    <hyperlink ref="E14" r:id="rId4" xr:uid="{FCAB122E-C52F-499B-B1B3-5FD7930FBF86}"/>
-    <hyperlink ref="E15" r:id="rId5" xr:uid="{68CA9956-446D-438E-BFCC-CEE68356A2B2}"/>
-    <hyperlink ref="E16" r:id="rId6" xr:uid="{CB252270-2C47-4959-923C-7EEE42E1FA8F}"/>
-    <hyperlink ref="E17" r:id="rId7" xr:uid="{E5415750-ADD2-478E-A108-FF9CD01F782B}"/>
-    <hyperlink ref="E19" r:id="rId8" xr:uid="{586E9A3B-F026-4380-99DE-E10FA082C864}"/>
-    <hyperlink ref="E22" r:id="rId9" xr:uid="{893992A6-F073-45AD-9173-AAB2912FFFD8}"/>
-    <hyperlink ref="E25" r:id="rId10" xr:uid="{F80F3465-60B2-46B4-A622-47A0EE99E4F4}"/>
-    <hyperlink ref="E27" r:id="rId11" xr:uid="{CE57DC7E-3446-41D4-8310-07743C7F793E}"/>
-    <hyperlink ref="E31" r:id="rId12" xr:uid="{5C6BBA9A-F1E7-4E98-BB24-C13A0A592D2C}"/>
-    <hyperlink ref="E33" r:id="rId13" xr:uid="{21B1B37D-2A8F-4D08-B8E9-D15B58DBF0B4}"/>
-    <hyperlink ref="E34" r:id="rId14" xr:uid="{23D7B77E-32A9-4823-802F-4BFE465623D3}"/>
-    <hyperlink ref="E36" r:id="rId15" xr:uid="{975FB611-8ED0-4172-B1B0-D162F3B12161}"/>
-    <hyperlink ref="D5" r:id="rId16" xr:uid="{1B25A455-653E-415A-ABAA-E1D30ECFA872}"/>
-    <hyperlink ref="D8" r:id="rId17" xr:uid="{54D70427-FD29-4E92-830D-78679C718AEE}"/>
-    <hyperlink ref="D16" r:id="rId18" xr:uid="{12669B36-82D6-4BE8-A84E-40BAE1D27A37}"/>
-    <hyperlink ref="D33" r:id="rId19" xr:uid="{25FB7C41-C08F-4959-97C3-E5F6E5A4D1C6}"/>
-    <hyperlink ref="D2" r:id="rId20" xr:uid="{518C36EF-5C9D-4A18-80A7-598BD3956244}"/>
-    <hyperlink ref="D30" r:id="rId21" xr:uid="{B84379DD-F2DC-404D-8CA2-4403A4DBFD5A}"/>
-    <hyperlink ref="D35" r:id="rId22" xr:uid="{FB56697B-C1A2-40F5-82FE-8E7CE59510C4}"/>
+    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink r:id="rId2" ref="D5"/>
+    <hyperlink r:id="rId3" ref="E5"/>
+    <hyperlink r:id="rId4" ref="D6"/>
+    <hyperlink r:id="rId5" ref="D7"/>
+    <hyperlink r:id="rId6" ref="D8"/>
+    <hyperlink r:id="rId7" ref="E9"/>
+    <hyperlink r:id="rId8" ref="D13"/>
+    <hyperlink r:id="rId9" ref="E13"/>
+    <hyperlink r:id="rId10" ref="E14"/>
+    <hyperlink r:id="rId11" ref="E15"/>
+    <hyperlink r:id="rId12" ref="D16"/>
+    <hyperlink r:id="rId13" ref="E16"/>
+    <hyperlink r:id="rId14" ref="E17"/>
+    <hyperlink r:id="rId15" ref="D19"/>
+    <hyperlink r:id="rId16" ref="E19"/>
+    <hyperlink r:id="rId17" ref="E22"/>
+    <hyperlink r:id="rId18" ref="E25"/>
+    <hyperlink r:id="rId19" ref="D27"/>
+    <hyperlink r:id="rId20" ref="E27"/>
+    <hyperlink r:id="rId21" ref="D29"/>
+    <hyperlink r:id="rId22" ref="D30"/>
+    <hyperlink r:id="rId23" ref="E31"/>
+    <hyperlink r:id="rId24" ref="D33"/>
+    <hyperlink r:id="rId25" ref="E33"/>
+    <hyperlink r:id="rId26" ref="E34"/>
+    <hyperlink r:id="rId27" ref="D35"/>
+    <hyperlink r:id="rId28" ref="E36"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId29"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4c164115-fe01-46e6-ac77-77420108489a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002BD4D40F3E2157448B0497B53CD94A5D" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="afa1714ce10ebb93488ebf1bf72be192">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4c164115-fe01-46e6-ac77-77420108489a" xmlns:ns3="93fc9c6d-4613-4fbb-a177-abcb402df3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b2159533906d9d949ede2d52b259ed3e" ns2:_="" ns3:_="">
-    <xsd:import namespace="4c164115-fe01-46e6-ac77-77420108489a"/>
-    <xsd:import namespace="93fc9c6d-4613-4fbb-a177-abcb402df3af"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4c164115-fe01-46e6-ac77-77420108489a" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f8ebb0a5-c57d-4c3a-bec7-8a38252dd05c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="17" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="18" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="19" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="20" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="22" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="93fc9c6d-4613-4fbb-a177-abcb402df3af" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40E27AEF-514B-4508-A5CA-BC79BEA3EFCF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4A73360-FF41-4A0B-BFF9-AEA7C835025E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3C7DBAB-E555-4E05-9BF7-3C1FD065566F}"/>
 </file>